--- a/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0001T0006Z000C1N30_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0001T0006Z000C1N30_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>8.801909482188984</v>
+        <v>1.43031029085571</v>
       </c>
       <c r="D2" t="n">
-        <v>12.06851942861861</v>
+        <v>1.961134407150525</v>
       </c>
       <c r="E2" t="n">
-        <v>5.225982762949662</v>
+        <v>0.8492221989793202</v>
       </c>
       <c r="F2" t="n">
-        <v>4.445289028597735</v>
+        <v>0.722359467147132</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>19.25387500808831</v>
+        <v>3.12875468881435</v>
       </c>
       <c r="D3" t="n">
-        <v>20.95909748581408</v>
+        <v>3.405853341444789</v>
       </c>
       <c r="E3" t="n">
-        <v>5.225982762949662</v>
+        <v>0.8492221989793202</v>
       </c>
       <c r="F3" t="n">
-        <v>4.445289028597735</v>
+        <v>0.722359467147132</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
